--- a/generated/spreadsheet/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area.xlsx
+++ b/generated/spreadsheet/planning-permission-for-relevant-demolition-in-a-conservation-area-demolition-con-area.xlsx
@@ -808,7 +808,7 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Planning requirement references identifying the information this document provides. A document may address more than one requirement. These references identify its coverage; they do not establish that the requirements have been satisfied.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Planning officer name</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -3414,7 +3414,7 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>A description of the development, works, change of use or reserved matters for which approval is sought</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
